--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_所得段階別の入力" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_保険料の対照" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_サービス別の対照" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_自己点検" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_人口の設定の入力値" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_自己点検" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -137,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,6 +211,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -602,6 +622,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -921,6 +942,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1341,6 +1363,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1627,6 +1650,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2168,6 +2192,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -2314,6 +2339,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2474,6 +2500,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -2580,6 +2607,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -2746,6 +2774,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2984,6 +3013,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -3144,6 +3174,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3684,7 +3715,1491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>「総人口と被保険者数の設定」に入れる値（案C）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="72" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>「独自データを登録する」を選んだ場合の入力値です。令和6年度・令和7年度は実績であるため画面の値をそのまま入れ、令和8年度以降を案C（総人口＝地方創生総合戦略、年齢階級別＝住民基本台帳の実績趨勢）に改めます。白い欄（6階級と第2号被保険者）が入力欄で、第1号被保険者と総数は自動計算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　総人口（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="25" t="inlineStr"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>案C（入力する値）</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>27303</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>27102</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>26940</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>26779</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>26619</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>26460</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>26232</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>25029</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>23821</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>22558</v>
+      </c>
+      <c r="M6" s="26" t="n">
+        <v>21271</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>画面の現在値</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>27303</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>27102</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>26876</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>26649</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>26422</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>26195</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>25969</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>24778</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>23582</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>22332</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>21058</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="11" t="inlineStr"/>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>差（案C−画面）</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>64</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>197</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>265</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>263</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>251</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>239</v>
+      </c>
+      <c r="L8" s="27" t="n">
+        <v>226</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2　被保険者数（1）男（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>876</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>845</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>829</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>834</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>839</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>844</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>850</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>883</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <v>1006</v>
+      </c>
+      <c r="L12" s="28" t="n">
+        <v>867</v>
+      </c>
+      <c r="M12" s="28" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>976</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>950</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>898</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <v>868</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>840</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>810</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>783</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>817</v>
+      </c>
+      <c r="K13" s="28" t="n">
+        <v>854</v>
+      </c>
+      <c r="L13" s="28" t="n">
+        <v>975</v>
+      </c>
+      <c r="M13" s="28" t="n">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>841</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>876</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>869</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>851</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>836</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>819</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>797</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>682</v>
+      </c>
+      <c r="K14" s="28" t="n">
+        <v>719</v>
+      </c>
+      <c r="L14" s="28" t="n">
+        <v>756</v>
+      </c>
+      <c r="M14" s="28" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>626</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>629</v>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>674</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>714</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>754</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>794</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>830</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>732</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>636</v>
+      </c>
+      <c r="L15" s="28" t="n">
+        <v>673</v>
+      </c>
+      <c r="M15" s="28" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>413</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>421</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>428</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>437</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>441</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>586</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>524</v>
+      </c>
+      <c r="L16" s="28" t="n">
+        <v>463</v>
+      </c>
+      <c r="M16" s="28" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>90歳以上</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>248</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>256</v>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>267</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>277</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>286</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>295</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>301</v>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>324</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>440</v>
+      </c>
+      <c r="L17" s="28" t="n">
+        <v>446</v>
+      </c>
+      <c r="M17" s="28" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>第2号被保険者</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>4442</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>4414</v>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>4373</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>4332</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>4249</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>4208</v>
+      </c>
+      <c r="J18" s="28" t="n">
+        <v>3929</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>3502</v>
+      </c>
+      <c r="L18" s="28" t="n">
+        <v>3167</v>
+      </c>
+      <c r="M18" s="28" t="n">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>第1号被保険者（自動）</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>3967</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>3956</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>3950</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>3965</v>
+      </c>
+      <c r="G19" s="29" t="n">
+        <v>3983</v>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>3999</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>4002</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>4024</v>
+      </c>
+      <c r="K19" s="29" t="n">
+        <v>4179</v>
+      </c>
+      <c r="L19" s="29" t="n">
+        <v>4180</v>
+      </c>
+      <c r="M19" s="29" t="n">
+        <v>4047</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>3　被保険者数（2）女（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>65〜69歳</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>895</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>847</v>
+      </c>
+      <c r="E23" s="28" t="n">
+        <v>841</v>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>854</v>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>867</v>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>882</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>897</v>
+      </c>
+      <c r="J23" s="28" t="n">
+        <v>962</v>
+      </c>
+      <c r="K23" s="28" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L23" s="28" t="n">
+        <v>873</v>
+      </c>
+      <c r="M23" s="28" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>70〜74歳</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>1072</v>
+      </c>
+      <c r="D24" s="28" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E24" s="28" t="n">
+        <v>974</v>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>928</v>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>882</v>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>836</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>793</v>
+      </c>
+      <c r="J24" s="28" t="n">
+        <v>870</v>
+      </c>
+      <c r="K24" s="28" t="n">
+        <v>934</v>
+      </c>
+      <c r="L24" s="28" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M24" s="28" t="n">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>75〜79歳</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D25" s="28" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E25" s="28" t="n">
+        <v>1057</v>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>1021</v>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>1002</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>977</v>
+      </c>
+      <c r="J25" s="28" t="n">
+        <v>764</v>
+      </c>
+      <c r="K25" s="28" t="n">
+        <v>842</v>
+      </c>
+      <c r="L25" s="28" t="n">
+        <v>906</v>
+      </c>
+      <c r="M25" s="28" t="n">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>80〜84歳</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n">
+        <v>899</v>
+      </c>
+      <c r="D26" s="28" t="n">
+        <v>896</v>
+      </c>
+      <c r="E26" s="28" t="n">
+        <v>946</v>
+      </c>
+      <c r="F26" s="28" t="n">
+        <v>989</v>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>1074</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J26" s="28" t="n">
+        <v>990</v>
+      </c>
+      <c r="K26" s="28" t="n">
+        <v>786</v>
+      </c>
+      <c r="L26" s="28" t="n">
+        <v>864</v>
+      </c>
+      <c r="M26" s="28" t="n">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>719</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <v>718</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>733</v>
+      </c>
+      <c r="F27" s="28" t="n">
+        <v>740</v>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>747</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>754</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>755</v>
+      </c>
+      <c r="J27" s="28" t="n">
+        <v>934</v>
+      </c>
+      <c r="K27" s="28" t="n">
+        <v>836</v>
+      </c>
+      <c r="L27" s="28" t="n">
+        <v>671</v>
+      </c>
+      <c r="M27" s="28" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>90歳以上</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>571</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>593</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>616</v>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>632</v>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>649</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>666</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>677</v>
+      </c>
+      <c r="J28" s="28" t="n">
+        <v>706</v>
+      </c>
+      <c r="K28" s="28" t="n">
+        <v>881</v>
+      </c>
+      <c r="L28" s="28" t="n">
+        <v>896</v>
+      </c>
+      <c r="M28" s="28" t="n">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>第2号被保険者</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>4786</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>4784</v>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>4729</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>4674</v>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>4620</v>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>4565</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>4510</v>
+      </c>
+      <c r="J29" s="28" t="n">
+        <v>4120</v>
+      </c>
+      <c r="K29" s="28" t="n">
+        <v>3601</v>
+      </c>
+      <c r="L29" s="28" t="n">
+        <v>3282</v>
+      </c>
+      <c r="M29" s="28" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="11" t="inlineStr"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>第1号被保険者（自動）</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>5191</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>5164</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>5167</v>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>5182</v>
+      </c>
+      <c r="G30" s="29" t="n">
+        <v>5196</v>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>5214</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>5209</v>
+      </c>
+      <c r="J30" s="29" t="n">
+        <v>5226</v>
+      </c>
+      <c r="K30" s="29" t="n">
+        <v>5312</v>
+      </c>
+      <c r="L30" s="29" t="n">
+        <v>5215</v>
+      </c>
+      <c r="M30" s="29" t="n">
+        <v>5080</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>4　入力後に画面が表示する値（自動計算）と現在値の対照</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="25" t="inlineStr"/>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>第1号被保険者 案C</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="n">
+        <v>9158</v>
+      </c>
+      <c r="D34" s="30" t="n">
+        <v>9120</v>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>9117</v>
+      </c>
+      <c r="F34" s="30" t="n">
+        <v>9147</v>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>9179</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <v>9213</v>
+      </c>
+      <c r="I34" s="30" t="n">
+        <v>9211</v>
+      </c>
+      <c r="J34" s="30" t="n">
+        <v>9250</v>
+      </c>
+      <c r="K34" s="30" t="n">
+        <v>9491</v>
+      </c>
+      <c r="L34" s="30" t="n">
+        <v>9395</v>
+      </c>
+      <c r="M34" s="30" t="n">
+        <v>9127</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者 画面</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>9158</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>9120</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>9117</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>9116</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>9110</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>9107</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>9106</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>9166</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>9375</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>9270</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>8993</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="11" t="inlineStr"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>差（案C−画面）</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>31</v>
+      </c>
+      <c r="G36" s="27" t="n">
+        <v>69</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>106</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>105</v>
+      </c>
+      <c r="J36" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="K36" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="L36" s="27" t="n">
+        <v>125</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>後期（75歳〜）の割合 案C</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="F37" s="31" t="n">
+        <v>0.6191</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="H37" s="31" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="I37" s="31" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="J37" s="31" t="n">
+        <v>0.6182</v>
+      </c>
+      <c r="K37" s="31" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="L37" s="31" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M37" s="31" t="n">
+        <v>0.648</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>同 画面</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>0.5957</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="F38" s="31" t="n">
+        <v>0.6067</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <v>0.6121</v>
+      </c>
+      <c r="H38" s="31" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="I38" s="31" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="J38" s="31" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="K38" s="31" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="L38" s="31" t="n">
+        <v>0.5853</v>
+      </c>
+      <c r="M38" s="31" t="n">
+        <v>0.6308</v>
+      </c>
+    </row>
+    <row r="39" ht="140" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>注1）令和6年度・令和7年度は実績であるため画面の値をそのまま入れます。令和8年度以降が案Cによる値です。
+注2）令和8年度の第1号被保険者数は案Cでも9,117人で画面と同じであり、動くのは年齢階級別の内訳だけです。
+注3）当方の案Cは65歳以上を65〜74歳・75〜84歳・85歳以上の3区分で推計しています。5歳階級への分け方と男女の分け方は、画面が現に表示している補正データの同じ年の構成比によっています。住民基本台帳の5歳階級の趨勢をそのまま延ばすと、65〜69歳が年▲4.2％・70〜74歳が年＋1.0％という特定の世代が移っていく動きをそのまま繰り返すことになり、令和11年度の65〜69歳の割合が0.41（画面は0.51）まで下がります。3区分より細かい構成は画面の側によるのが妥当と考えます。
+注4）第2号被保険者（40歳から64歳）は画面の値をそのままとしています。案Cは総人口と65歳以上の趨勢を定めるもので、40歳から64歳の内訳を持っていません。第1号被保険者の保険料の算定には用いられません。
+注5）後期高齢者の割合が画面より高くなります（令和11年度 0.6340対0.6174）。調整交付金の後期高齢者加入割合補正係数が上がるため、調整交付金見込額が増え保険料を下げる向きに働きます。一方で認定者数が増えるため給付費は上がる向きに働きます。どちらが上回るかは入力後の算定によります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>5　併せて入れ直すもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>入れ直す内容</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別第1号被保険者数①（標準段階区分）</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>計が案Cの第1号被保険者数（9,147／9,179／9,213／9,211／9,250／9,491／9,395／9,127人）になる表に入れ直す。これにより加入割合の合計が全年度で1.0000になる</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別第1号被保険者数②（弾力化）</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>当連合の条例による16段階で入れる。①と②の計は同じ第1号被保険者数にそろえる</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>実績及び推計方法の設定（認定率・利用率の伸び）</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>「令和6年度→令和7年度の伸び」のままでよい（変更は要らない）</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>保険料額の算定（保険料収納必要額）</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費を入れる。人口の設定とは別の作業である</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>注）人口の設定を改めると、認定者数・サービス見込量・給付費・保険料のすべてが計算し直されます。所得段階別の表を入れ直さないと、加入割合の合計が1.0にならない状態が残ります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A10:M10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L見える化システムの推計結果の受領点検（令和8年9月30日）&amp;R&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4187,50 +5702,225 @@
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>画面の被保険者数の読み取りが受領した出力と一致すること</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>6階級の和＝1_推計値サマリの第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第10期3か年 [9116, 9110, 9107]／受領 [9116, 9110, 9107]</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>画面の第1号＋第2号が受領した出力の総数と一致すること</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>第1号＋第2号（男女計）＝1_推計値サマリの総数</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>R6 18386人</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>案Cの入力値の和が当方の推計と一致すること（整数化で合計を保つ）</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>男6階級＋女6階級の和 ＝ 案Cの65歳以上</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>合わない年度 なし</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度は画面の値をそのまま用いていること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>実績年の入力値＝画面の値</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>変えている年度 なし</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度の第1号被保険者数が当方の算定と一致すること</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>案Cの令和11年度 ＝ 9,213人</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>9213人</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者の割合が画面より高くなること（案Cの趨勢による）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>75歳以上÷65歳以上を第10期3か年で比べる</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>案C [0.6191, 0.6265, 0.634]／画面 [0.6067, 0.6121, 0.6174]</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>強調の指定（）がセルに残っていないこと</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>全シートの全セルを走査（xlsx は Markdown を解釈しない）</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>個人を特定する値を収めていないこと</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>担当者名・電話番号・メールアドレスの形を走査</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>電話番号・メールアドレスの形を全セルで走査</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="25" t="inlineStr"/>
-      <c r="B24" s="25" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="25" t="inlineStr"/>
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr"/>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>適合19件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr"/>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>適合26件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>注）本シートが確かめているのは受領した推計結果の内的整合と、本表がそれを正しく読み取れていることです。推計そのものの当否を確かめるものではありません。</t>
         </is>
@@ -4240,7 +5930,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_保険料の対照" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_サービス別の対照" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_人口の設定の入力値" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_自己点検" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_弾力化の入力値" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_自己点検" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -139,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,6 +230,24 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -911,6 +930,858 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>自己点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="72" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本表の内的整合を機械で確かめた記録です。1件でも不適合があると出力そのものを止めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>点検した内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>式・条件</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>第9期の保険料基準額が当方の再現と1円以内で一致すること</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>|見える化 − 当方の再現6,427.92| &lt; 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>見える化 6427.8896円／当方 6,427.92円</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納必要額が内訳から再現できること</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>第1号負担分＋調整交付金相当額−調整交付金見込額</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>再現 2108094699.08円／記載 2108094699.08円</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>5シートの月額が所得段階別の入力と標準13段階の割合から再現できること</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>J÷0.99÷補正後被保険者数÷12</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>再現 6599.5114円／記載 6599.5114円</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者負担分相当額が標準給付費見込額の23％であること</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>（標準給付費見込額＋地域支援事業費）×0.23</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2346670038.53円／0.23倍は 2346670038.53円</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額が内訳の和と一致すること</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>総給付費＋特定入所者＋高額＋高額医療合算＋審査支払手数料</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>内訳の和 10202913211円／記載 10202913211円</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費が0であること（未入力であることの確認）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>5_保険料推計 地域支援事業費</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>加入割合の合計が1.0にならない年度を拾えていること</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>|加入割合の合計 − 1| &gt; 0.000001 の年度</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>該当 R12・R17・R22・R27・R32</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>第10期の所得段階別の計が画面の第1号被保険者数と一致すること</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の計 ＝ 画面の第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>合わない年度 なし</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>令和12年度以降の所得段階別の計が画面の第1号被保険者数と違うこと</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の計 ≠ 画面の第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>一致してしまう年度 なし</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の段階ごとの和が計と一致すること</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Σ第1〜13段階 ＝ 計</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>合わない年度 なし</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1シートと5シートの保険料基準額が違うこと（2通りあることの確認）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>1_推計値サマリ 第10期 ≠ 5_保険料推計 第10期</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>6907.3631円／6599.5114円</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の人数の欄が全て整数であること</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>非ゼロの区分について小数部が0</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>非ゼロ32件／整数32件</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度の人数の欄に小数があること（月平均であることの確認）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>非ゼロの区分について小数部が0でないものがある</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>非ゼロ36件／小数31件</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度が令和7年度と±10％超ずれる区分を拾えていること</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>|R8／R7 − 1| &gt; 0.10</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>18件</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度が0で令和11年度も0のままの区分があること</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>R8＝0 かつ R11＝0</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>4件（介護予防短期入所療養介護（老健）・介護予防認知症対応型共同生活介護・住宅改修費・定期巡回・随時対応型訪問介護看護）</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>設定の対照が受領した設定を残らず判定していること</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>判定が「―」のものがないこと。要改の件数</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>8件／判定なし 0件／要改 3件</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定の月額が算定スクリプトの値と一致すること</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>build による算定値をそのまま用いている</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>6436.09円</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>弾力化にした場合の月額が標準13段階より低くなること</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>条例16段階の乗率は標準より補正後被保険者数が大きくなる</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>13段階 6599.51円／16段階 6548.75円</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>画面の被保険者数の読み取りが受領した出力と一致すること</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>6階級の和＝1_推計値サマリの第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第10期3か年 [9116, 9110, 9107]／受領 [9116, 9110, 9107]</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>画面の第1号＋第2号が受領した出力の総数と一致すること</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>第1号＋第2号（男女計）＝1_推計値サマリの総数</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>R6 18386人</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>案Cの入力値の和が当方の推計と一致すること（整数化で合計を保つ）</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>男6階級＋女6階級の和 ＝ 案Cの65歳以上</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>合わない年度 なし</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度は画面の値をそのまま用いていること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>実績年の入力値＝画面の値</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>変えている年度 なし</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度の第1号被保険者数が当方の算定と一致すること</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>案Cの令和11年度 ＝ 9,213人</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>9213人</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者の割合が画面より高くなること（案Cの趨勢による）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>75歳以上÷65歳以上を第10期3か年で比べる</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>案C [0.6191, 0.6265, 0.634]／画面 [0.6067, 0.6121, 0.6174]</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>画面に入力済みの16段階の人数が当方の値と一致すること</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>弾力化②の画面の写し ＝ 所得段階別の将来推計（案C）</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>全8年度×16段階＝128件／違い なし</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>画面の段階別の和が画面の「計」の行と一致すること</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>読み取りの検算（Σ第1〜16段階 ＝ 計）</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>全8年度／合わない なし</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>基準所得金額が第7段階から第16段階の10件で昇順であること</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>第1〜6段階は欄なし／第7段階以降は金額かつ昇順</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>欄なし 第1・2・3・4・5・6段階／金額10件（1,200,000〜10,200,000円）</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>条例の割合が標準13段階と違う段階を拾えていること</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>第1〜13段階で 条例の割合 ≠ 標準の割合 となる段階を数える</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>違う 9段階（第2・4・6・7・8・9・11・12・13段階）／標準にない 第14〜16段階</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>強調の指定（）がセルに残っていないこと</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>全シートの全セルを走査（xlsx は Markdown を解釈しない）</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>個人を特定する値を収めていないこと</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>電話番号・メールアドレスの形を全セルで走査</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="25" t="inlineStr"/>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>自己点検の結果</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr"/>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>適合30件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E35" s="38" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>注）本シートが確かめているのは受領した推計結果の内的整合と、本表がそれを正しく読み取れていることです。推計そのものの当否を確かめるものではありません。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A36:E36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L見える化システムの推計結果の受領点検（令和8年9月30日）&amp;R&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5199,738 +6070,855 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>自己点検</t>
+          <t>「②保険料基準額に対する割合の弾力化」に入れる基準所得金額と割合</t>
         </is>
       </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本表の内的整合を機械で確かめた記録です。1件でも不適合があると出力そのものを止めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>点検した内容</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>式・条件</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>第9期の保険料基準額が当方の再現と1円以内で一致すること</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>|見える化 − 当方の再現6,427.92| &lt; 1</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>見える化 6427.8896円／当方 6,427.92円</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>画面には既に所得段階別第1号被保険者数（16段階）が入っており、未入力は基準所得金額と基準額に対する割合の2つです。本シートはその2つに入れる値です。基準所得金額は第7段階から第16段階の10件、割合は16段階すべてで、いずれも年度によらず同じ値です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　基準所得金額と基準額に対する割合（全年度共通）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>対象者要件</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>割合</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>基準所得金額（円）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>画面の現在値</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>標準13段階の割合</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>保険料収納必要額が内訳から再現できること</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>第1号負担分＋調整交付金相当額−調整交付金見込額</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>再現 2108094699.08円／記載 2108094699.08円</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>生活保護受給者、世帯全員住民税非課税で老齢福祉年金受給者又は合計所得金額＋課税年金収入額80万円以下</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>公費軽減の対象（割合は軽減前）／基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>5シートの月額が所得段階別の入力と標準13段階の割合から再現できること</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>J÷0.99÷補正後被保険者数÷12</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>再現 6599.5114円／記載 6599.5114円</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>世帯全員住民税非課税で、合計所得金額＋課税年金収入額80万円超120万円以下</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>公費軽減の対象（割合は軽減前）／標準と違う／基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>第1号被保険者負担分相当額が標準給付費見込額の23％であること</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>（標準給付費見込額＋地域支援事業費）×0.23</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>2346670038.53円／0.23倍は 2346670038.53円</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>世帯全員住民税非課税で、合計所得金額＋課税年金収入額120万円超</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>公費軽減の対象（割合は軽減前）／基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>標準給付費見込額が内訳の和と一致すること</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>総給付費＋特定入所者＋高額＋高額医療合算＋審査支払手数料</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>内訳の和 10202913211円／記載 10202913211円</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>住民税課税世帯で本人非課税、合計所得金額＋課税年金収入額80万円以下</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う／基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費が0であること（未入力であることの確認）</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>5_保険料推計 地域支援事業費</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>住民税課税世帯で本人非課税、合計所得金額＋課税年金収入額80万円超（基準額）</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>加入割合の合計が1.0にならない年度を拾えていること</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>|加入割合の合計 − 1| &gt; 0.000001 の年度</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>該当 R12・R17・R22・R27・R32</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額120万円未満</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う／基準所得金額の欄なし</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>第10期の所得段階別の計が画面の第1号被保険者数と一致すること</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別の計 ＝ 画面の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>合わない年度 なし</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額120万円以上210万円未満</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>令和12年度以降の所得段階別の計が画面の第1号被保険者数と違うこと</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別の計 ≠ 画面の第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>一致してしまう年度 なし</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額210万円以上320万円未満</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の段階ごとの和が計と一致すること</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Σ第1〜13段階 ＝ 計</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>合わない年度 なし</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額320万円以上420万円未満</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>1シートと5シートの保険料基準額が違うこと（2通りあることの確認）</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>1_推計値サマリ 第10期 ≠ 5_保険料推計 第10期</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>6907.3631円／6599.5114円</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
+          <t>本人住民税課税、合計所得金額420万円以上520万円未満</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の人数の欄が全て整数であること</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>非ゼロの区分について小数部が0</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>非ゼロ32件／整数32件</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額520万円以上620万円未満</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の人数の欄に小数があること（月平均であることの確認）</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>非ゼロの区分について小数部が0でないものがある</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>非ゼロ36件／小数31件</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額620万円以上720万円未満</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>令和8年度が令和7年度と±10％超ずれる区分を拾えていること</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>|R8／R7 − 1| &gt; 0.10</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>18件</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額720万円以上820万円未満</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>標準と違う</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>令和8年度が0で令和11年度も0のままの区分があること</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>R8＝0 かつ R11＝0</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>4件（介護予防短期入所療養介護（老健）・介護予防認知症対応型共同生活介護・住宅改修費・定期巡回・随時対応型訪問介護看護）</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額820万円以上920万円未満</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>多段階化した分。標準13段階にない</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>設定の対照が受領した設定を残らず判定していること</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>判定が「―」のものがないこと。要改の件数</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>8件／判定なし 0件／要改 3件</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
+          <t>本人住民税課税、合計所得金額920万円以上1,020万円未満</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>多段階化した分。標準13段階にない</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>当方の算定の月額が算定スクリプトの値と一致すること</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>build による算定値をそのまま用いている</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>6436.09円</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>弾力化にした場合の月額が標準13段階より低くなること</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>条例16段階の乗率は標準より補正後被保険者数が大きくなる</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>13段階 6599.51円／16段階 6548.75円</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>画面の被保険者数の読み取りが受領した出力と一致すること</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>6階級の和＝1_推計値サマリの第1号被保険者数</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>第10期3か年 [9116, 9110, 9107]／受領 [9116, 9110, 9107]</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>画面の第1号＋第2号が受領した出力の総数と一致すること</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>第1号＋第2号（男女計）＝1_推計値サマリの総数</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>R6 18386人</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>案Cの入力値の和が当方の推計と一致すること（整数化で合計を保つ）</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>男6階級＋女6階級の和 ＝ 案Cの65歳以上</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>合わない年度 なし</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
+          <t>本人住民税課税、合計所得金額1,020万円以上</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>多段階化した分。標準13段階にない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="140" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>注1）割合は公費軽減前の値です。第1段階から第3段階は公費軽減の対象ですが、補正後被保険者数はこの割合で算定します。見える化システムが「①標準段階区分・割合」の画面に表示する0.4550・0.6850・0.6900…も公費軽減前の値であり、基準がそろっています。公費軽減後の値（第1段階0.285など）は入れません。
+注2）基準所得金額は第7段階から第16段階の10件です。第1段階から第6段階は本人の合計所得金額の下限による区分ではないため（生活保護受給・世帯の課税状況・合計所得金額＋課税年金収入額による）画面も当該欄を受け付けません。第7段階から第13段階の額は画面が標準として表示している額と一致し、第14段階から第16段階が多段階化した分です。
+注3）割合は9つの段階で標準13段階と違い、第14段階から第16段階は標準にありません。これが弾力化を要する理由です。
+注4）第10期の段階数・割合・基準所得金額は政令改正により変わり得ます（確認事項No.33）。令和8年3月の全国課長会議資料は、保険料段階の基準額を80.9万円から82.65万円に改める政令改正が済んでおり、条例改正の手続を要するとしています。本表は第9期の条例による暫定の値です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2　画面に入力済みの第1号被保険者数と当方の値の対照（人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>画面の計</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>当方の計（案C）</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>段階別</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度は画面の値をそのまま用いていること</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>実績年の入力値＝画面の値</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>変えている年度 なし</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>9147</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>9147</v>
+      </c>
+      <c r="E26" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>19.5</v>
+        <v>2</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>令和11年度の第1号被保険者数が当方の算定と一致すること</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>案Cの令和11年度 ＝ 9,213人</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>9213人</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>9179</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>9179</v>
+      </c>
+      <c r="E27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="n">
-        <v>19.6</v>
+        <v>3</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>後期高齢者の割合が画面より高くなること（案Cの趨勢による）</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>75歳以上÷65歳以上を第10期3か年で比べる</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>案C [0.6191, 0.6265, 0.634]／画面 [0.6067, 0.6121, 0.6174]</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>9213</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>9213</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>強調の指定（）がセルに残っていないこと</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>全シートの全セルを走査（xlsx は Markdown を解釈しない）</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>9211</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>9211</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>個人を特定する値を収めていないこと</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>電話番号・メールアドレスの形を全セルで走査</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>0件</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="25" t="inlineStr"/>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>自己点検の結果</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr"/>
-      <c r="D31" s="25" t="inlineStr">
-        <is>
-          <t>適合26件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>適合</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>注）本シートが確かめているのは受領した推計結果の内的整合と、本表がそれを正しく読み取れていることです。推計そのものの当否を確かめるものではありません。</t>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>9250</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>9250</v>
+      </c>
+      <c r="E30" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>9491</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>9491</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>令和27年度</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>9395</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>9395</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>令和32年度</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>9127</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>9127</v>
+      </c>
+      <c r="E33" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>画面の計＝段階別の和</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="104" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>注1）画面に入っている16段階の人数は、当方が人口の設定（案C）からお示しした値と全年度・全段階で一致しています。人数の入れ直しは要りません。第10期と令和12年度以降が同じ人口の系列でそろっており、01シートに掲げた「第10期と令和12年度以降で別の人口による」（加入割合の合計が1.0を超える）は、この画面では解消しています。
+注2）画面の上部に表示されている保険料額は暫定値であり、従前の写しから動いています（第10期 6,907円から6,691円、令和12年度以降 7,882円から7,574円）。地域支援事業費が0のままであることなど、01シートの修正が済むまでは当方の算定と突き合わせられません。
+注3）第17段階から第30段階は空欄のままとします（当連合の所得段階は16段階です）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:E32"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -16,7 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_サービス別の対照" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_人口の設定の入力値" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_弾力化の入力値" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_自己点検" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_再出力の点検" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ワーニングチェック" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_自己点検" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -247,6 +249,21 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -936,7 +953,2714 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>人口の設定を案Cに改めた後の再出力の点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="72" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/30受領。推計パターン 9028（１）。人口の設定を案Cに改めた後の出力を、改める前の出力及び当方の算定と突き合わせたものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　人口の設定の変更が及んでいる箇所・及んでいない箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>改める前</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>改めた後</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>第1号被保険者数（第10期3か年）</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>27,333人</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>27,539人</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>+206人</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>案Cに変わった。当方の算定と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者加入割合補正係数（令和11年度）</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>0.9231</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>0.8967</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>-0.0264</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>後期高齢者の割合が上がったため下がった</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>調整交付金見込額（第10期3か年）</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>748,721,000円</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>801,152,000円</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>+52,431,000円</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>増えた。保険料を下げる向きに働く</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納必要額（第10期3か年）</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>2,108,094,699円</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>2,055,663,699円</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>-52,430,999円</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>減った額は調整交付金の増加額と一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>要介護（支援）認定者数（令和11年度・第1号）</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>2,031人</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>2,031人</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>±0人</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>人口が変わったのに1人も動いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>総給付費（第10期3か年）</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>9,685,143千円</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>9,685,143千円</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>±0千円</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>標準給付費見込額（第10期3か年）</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>10,202,913,211円</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>10,202,913,211円</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>±0円</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>注1）人口の設定の変更は、第1号被保険者数と調整交付金にしか及んでいません。認定者数・サービス見込量・総給付費・標準給付費見込額は改める前の出力と1円も変わっていません。認定者数は8年度すべてで同じ値です。
+注2）認定者数は性別・年齢5歳階級別・要介護度別の認定率に将来人口を乗じて推計するものであり、人口が変われば認定者数も変わります。「実績及び推計方法の設定」を保存したうえで、施策反映（認定者数）→（施設・居住系）→（在宅）→ 地域支援事業 →保険料額の算定 の順に各画面を開いて登録し直すことを要します。登録し直せたかどうかは、令和11年度の認定者数（第1号）が2,031人から変わることで確かめられます。
+注3）保険料収納必要額の減少額52,430,999円は、調整交付金見込額の増加額と円単位で一致します。給付費の側が動いていないことの裏づけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2　修正が必要な箇所11件の現況</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>修正が必要な箇所</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>前回</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>保険料基準額が同じ出力の中で2通りある</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1シート6,907円／5シート6,600円</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1シートも5シートも6,387円</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別が登録されたため一致した</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の計が第10期と令和12年度以降で別の人口による</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>加入割合の合計が最大1.0149</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>全8年度とも1.0000</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別加入割合補正係数も全8年度0.9856にそろった</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>人口の設定が社人研のまま</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>社人研</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>案C</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>ただし給付費の側へ及んでいない（本シート1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費が全ての欄で0</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>当方の第10期3か年531,483,777円。月額 約+333円</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>所得段階を弾力化していない</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>標準13段階</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>標準13段階</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>条例は16段階。月額 約-49円</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値を編集していない</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>月報からの計算値のまま</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>月報からの計算値のまま</t>
+        </is>
+      </c>
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>ワーニング36件のうち15件がこれによる（10シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費の実績値が令和8年度</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.137。ワーニング3件がこれによる</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス利用者数の自然体推計手法が包括推計</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>包括推計</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>包括推計</t>
+        </is>
+      </c>
+      <c r="E24" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.126。当方は要介護度別</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>準備基金が0</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="E25" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度末の基金残高の提供を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金の欄が0</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>0円</t>
+        </is>
+      </c>
+      <c r="E26" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.86。Bを入れるときに二重控除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>施策反映の記入欄が空欄</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>「出力後に入力」のまま</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>「出力後に入力」のまま</t>
+        </is>
+      </c>
+      <c r="E27" s="38" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>計画に載せる前に記入を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>注）11件のうち3件が解消し、8件が残っています。残る8件のうち月額を動かすのは、地域支援事業費・弾力化・令和8年度の実績見込み値・1人1月あたり給付費の年度・準備基金の5件です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>3　保険料基準額（月額）の見通し</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>置き方</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>補正後被保険者数</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>月額</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>現況との差</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>現況（標準13段階・地域支援事業費0）</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>27089.7</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>6387.51</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>+0円</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>出力の値6387.25円と0.26円の差</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>弾力化のみ（条例16段階）</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>27298.8</v>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>6338.59</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>-49円</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>条例の割合による</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費のみ</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>27089.7</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>6720.22</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>+333円</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>当方のB 531,483,777円</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>弾力化＋地域支援事業費</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>27298.8</v>
+      </c>
+      <c r="D35" s="39" t="n">
+        <v>6668.76</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>+281円</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>この2件を入れた場合の見通し</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="inlineStr"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>（参考）当方の算定</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="n">
+        <v>27301.18914210633</v>
+      </c>
+      <c r="D36" s="41" t="n">
+        <v>6436.09138225251</v>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>+49円</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>令和7年度基準・要介護度別・地域支援事業費を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>注1）本シートの月額は保険料収納必要額2,055,663,699円から計算したものです。地域支援事業費を入れた行は、当方のB（531,483,777円）を3か年に均等に置き、年度別の調整交付金見込交付割合で第1号負担分を求めたものです。
+注2）現況と当方の算定の差は、地域支援事業費・弾力化を入れてもなお残ります。残る差は、基準年度が令和8年度であること（確認事項No.137）、包括推計であること（同No.126）、給付費の側が人口の変更を受けていないこと（本シート1）によります。
+注3）いずれも暫定値です。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L見える化システムの推計結果の受領点検（令和8年9月30日）&amp;R&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>将来推計ワーニングチェック結果の点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="72" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/30受領。施策反映の3画面（認定者数・施設居住系・在宅）はいずれも該当無しであり、ワーニングは参考として示される39件に限られます。それぞれについて、当方の年報令和7年度の値と突き合わせ、手当てを要するかどうかを判定しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　サービス別の要約</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>要因</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回（日）数（在宅）</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>当区域の実態</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>当方の年報令和7年度でも要介護計55.4回／月で全国の上限50回を上回ります。訪問介護の利用回数が多いことは当区域の実態であり、入力の誤りではありません。理由を記入して進めます</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回（日）数（在宅）</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>利用回（日）数が0のまま令和9年度以降も0で残っています。当方の年報令和7年度は要介護計7.9回／月です</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費（居住系）</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費の年度</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>当方の年報令和7年度は要介護5で238,772円／月です。画面の350,399円／月は令和8年度（月報4〜7月）によるものとみられます（確認事項No.137）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回（日）数（在宅）</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>当方の年報令和7年度は要介護計6.3回／月で閾値の範囲内です。令和8年度（月報4〜7月）の値が使われていることによります</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回（日）数（在宅）</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>当方の年報令和7年度は要支援7.9日／月で閾値の範囲内です。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回（日）数（在宅）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>当方の年報令和7年度は要介護計7.9回／月であり、画面の34.3〜36.2回／月は4倍を超えます。月に31回を超える値であり、そのままでは用いられません</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="22" t="inlineStr"/>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="n">
+        <v>39</v>
+      </c>
+      <c r="D12" s="22" t="inlineStr"/>
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>注1）ワーニングは推計を止めるものではありません。全国の分布から定めた閾値との対比であり、外れていても理由が説明できれば進められます。施策反映の3画面（推計そのもの）は該当無しです。
+注2）39件のうち18件（訪問介護）は当区域の実態です。当方の年報令和7年度でも要介護計55.4回／月で全国の上限50回を上回ります。手当ては要しません。
+注3）残る21件は令和8年度の実績見込み値と1人1月あたり給付費の年度によるものです（確認事項No.128・No.137）。令和7年度の値に差し替えれば解消する見込みです。とくに地域密着型通所介護は月に31回を超える値になっており、そのままでは用いられません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2　ワーニングの明細（39件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>要介護度</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>画面の値</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>当方（年報R7）</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>350399</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>238,772</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>上限値を¥56,534上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>350399</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>238,772</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>上限値を¥56,534上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>350399</v>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>238,772</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>上限値を¥56,534上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>上限値を4.6回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>上限値を11.3回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>上限値を9.9回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>上限値を11.0回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>上限値を2.2回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>上限値を13.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>上限値を4.6回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>上限値を11.4回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>上限値を8.7回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>上限値を10.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>上限値を4.1回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>上限値を13.6回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>上限値を4.6回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>上限値を11.4回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>上限値を7.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>上限値を9.9回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>上限値を5.9回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>上限値を13.4回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.5回上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.4日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.4日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>上限値を1.4日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>上限値を6.3日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>上限値を7.3日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>上限値を8.2日上回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>下限値を2.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>下限値を2.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>下限値を2.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり利用回</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>下限値を1.0回下回っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>注1）「当方（年報R7）」は要支援計・要介護計の値であり、要介護度別ではありません。当方は1人1月あたり回（日）数を要支援・要介護の2区分で固定しているためです。
+注2）特定施設入居者生活介護は1人1月あたり給付費（円）、そのほかは1人1月あたり利用回（日）数です。
+注3）認知症対応型通所介護は画面の値が0であり、下限を下回るものとして挙がっています。区域内に事業所はありませんが区域外の事業所で給付があり、当方は令和11年度に月1.05人と算定しています。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L見える化システムの推計結果の受領点検（令和8年9月30日）&amp;R&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1689,21 +4413,21 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>強調の指定（）がセルに残っていないこと</t>
+          <t>再出力の第1号被保険者数が当方の案Cと一致すること</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>全シートの全セルを走査（xlsx は Markdown を解釈しない）</t>
+          <t>総括表 1．被保険者数 ＝ 所得段階別の将来推計の計</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>全8年度／合わない なし</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -1714,50 +4438,225 @@
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>人口の設定を改めても認定者数・総給付費が変わっていないこと</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>改める前の出力と改めた後の出力を8年度で突き合わせる</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>認定者数・総給付費とも全8年度で同じ／違い なし</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納必要額の減少額が調整交付金見込額の増加額と一致すること</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>給付費の側が動いていないことの裏づけ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>収納必要額 ▲52,431,000円／調整交付金 +52,431,000円</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>標準13段階で再現した月額が出力の月額と1円以内で一致すること</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>保険料収納必要額÷0.99÷補正後被保険者数÷12</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>再現 6387.51円／出力 6387.25円</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>画面に登録されている所得段階別が当方の標準13段階の値と一致すること</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>総括表 5．所得段階別被保険者数 ＝ 08シート2（13段階へ束ねる案）</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>全8年度×13段階＝104件／違い なし</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>施策反映の3画面にワーニングがないこと</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>認定者数・施設居住系・在宅の3画面の件数</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>該当のあるもの なし</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>ワーニングの明細の件数が概要の件数と一致すること</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>概要の件数の和 ＝ 明細の行数</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>概要 39件／明細 39件</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>強調の指定（）がセルに残っていないこと</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>全シートの全セルを走査（xlsx は Markdown を解釈しない）</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>0件</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>個人を特定する値を収めていないこと</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>電話番号・メールアドレスの形を全セルで走査</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="25" t="inlineStr"/>
-      <c r="B35" s="25" t="inlineStr">
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="25" t="inlineStr"/>
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr"/>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>適合30件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr"/>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>適合37件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>注）本シートが確かめているのは受領した推計結果の内的整合と、本表がそれを正しく読み取れていることです。推計そのものの当否を確かめるものではありません。</t>
         </is>
@@ -1767,7 +4666,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A43:E43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>6,436円</t>
+          <t>6,438円</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1765,11 +1765,11 @@
         <v>27301.18914210633</v>
       </c>
       <c r="D36" s="41" t="n">
-        <v>6436.09138225251</v>
+        <v>6438.255719340626</v>
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
-          <t>+49円</t>
+          <t>+51円</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>build による算定値をそのまま用いている</t>
+          <t>build による算定値をそのまま用いている（固定値で突き合わせない）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>6436.09円</t>
+          <t>6438.26円（保険料基準額 6400円）</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -6471,7 +6471,7 @@
         <v>27301.2</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>6436.09</v>
+        <v>6438.26</v>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
@@ -6597,10 +6597,10 @@
         <v>9685143000</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>9031900444</v>
+        <v>9035114142</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>653242556</v>
+        <v>650028858</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
         <v>10202913211</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>9565616321</v>
+        <v>9569019924</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>637296890</v>
+        <v>633893287</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
         <v>2346670039</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2322333022</v>
+        <v>2323115851</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>24337016</v>
+        <v>23554187</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -6693,10 +6693,10 @@
         <v>510145661</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>494350214</v>
+        <v>494520394</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>15795447</v>
+        <v>15625267</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -6717,10 +6717,10 @@
         <v>748721000</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>729213412</v>
+        <v>729464444</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>19507588</v>
+        <v>19256556</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -6741,10 +6741,10 @@
         <v>2108094699</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>2087469824</v>
+        <v>2088171801</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>20624875</v>
+        <v>19922898</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
@@ -6763,10 +6763,10 @@
         <v>6599.51</v>
       </c>
       <c r="D13" s="23" t="n">
-        <v>6436.09</v>
+        <v>6438.26</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>163.42</v>
+        <v>161.26</v>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>

--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -1389,7 +1389,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>当方の第10期3か年531,483,777円。月額 約+333円</t>
+          <t>当方の第10期3か年531,483,777円。月額 約＋333円</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>条例は16段階。月額 約-49円</t>
+          <t>条例は16段階。月額 約▲49円</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>ワーニング36件のうち15件がこれによる（10シート）</t>
+          <t>ワーニング39件のうち18件がこれによる（10シート）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_見える化_推計結果の受領点検.xlsx
+++ b/output/第10期計画_見える化_推計結果の受領点検.xlsx
@@ -4117,12 +4117,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>当方の算定の月額が算定スクリプトの値と一致すること</t>
+          <t>当方の算定の月額が本計画の算定の値と一致すること</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>build による算定値をそのまま用いている（固定値で突き合わせない）</t>
+          <t>算定の値をそのまま用いている</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
